--- a/Data/EXCEL/Transfer/salemon/20240711/6813-salemon-20240711.xlsx
+++ b/Data/EXCEL/Transfer/salemon/20240711/6813-salemon-20240711.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlsx\20240711\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\GithubProjects\GoodinfoData2DB\Data\EXCEL\Transfer\salemon\20240711\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FB225987-31F0-433C-B61D-DDFE799A124C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B7A201F2-D192-4137-A808-136F112C4559}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="900" yWindow="290" windowWidth="18240" windowHeight="13390" xr2:uid="{E2E9C22C-0851-4054-8F53-08457DFB85B7}"/>
+    <workbookView xWindow="768" yWindow="684" windowWidth="20004" windowHeight="13956" xr2:uid="{E26EEA16-D938-4D1C-A437-FCA17144B757}"/>
   </bookViews>
   <sheets>
     <sheet name="6813-salemon-20240711" sheetId="2" r:id="rId1"/>
@@ -1261,16 +1261,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1BFD52E6-97C7-4805-97FB-835F5F3DFF7D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DE73D14-E7D4-4042-9ECE-E455229B6490}">
   <dimension ref="A1:Q97"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.54296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="7" width="5.08984375" bestFit="1" customWidth="1"/>
-    <col min="8" max="17" width="5.36328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="7" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="17" width="5.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
@@ -1297,7 +1297,7 @@
       <c r="P1" s="19"/>
       <c r="Q1" s="20"/>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A2" s="16"/>
       <c r="B2" s="15" t="s">
         <v>4</v>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="Q2" s="20"/>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A3" s="16"/>
       <c r="B3" s="16"/>
       <c r="C3" s="16"/>
@@ -1379,7 +1379,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A4" s="17"/>
       <c r="B4" s="17"/>
       <c r="C4" s="17"/>
@@ -1418,7 +1418,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A5" s="5">
         <v>45444</v>
       </c>
@@ -1471,7 +1471,7 @@
         <v>222.7</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A6" s="9">
         <v>45413</v>
       </c>
@@ -1524,7 +1524,7 @@
         <v>213.8</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A7" s="5">
         <v>45383</v>
       </c>
@@ -1577,7 +1577,7 @@
         <v>208.7</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A8" s="9">
         <v>45352</v>
       </c>
@@ -1630,7 +1630,7 @@
         <v>192.7</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A9" s="5">
         <v>45323</v>
       </c>
@@ -1683,7 +1683,7 @@
         <v>128.19999999999999</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A10" s="9">
         <v>45292</v>
       </c>
@@ -1736,7 +1736,7 @@
         <v>58.2</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A11" s="5">
         <v>45261</v>
       </c>
@@ -1789,7 +1789,7 @@
         <v>-32.4</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A12" s="9">
         <v>45231</v>
       </c>
@@ -1842,7 +1842,7 @@
         <v>-31.1</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A13" s="5">
         <v>45200</v>
       </c>
@@ -1895,7 +1895,7 @@
         <v>-36.6</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A14" s="9">
         <v>45170</v>
       </c>
@@ -1948,7 +1948,7 @@
         <v>-40.5</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A15" s="5">
         <v>45139</v>
       </c>
@@ -2001,7 +2001,7 @@
         <v>-41</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A16" s="9">
         <v>45108</v>
       </c>
@@ -2054,7 +2054,7 @@
         <v>-43.6</v>
       </c>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A17" s="5">
         <v>45078</v>
       </c>
@@ -2107,7 +2107,7 @@
         <v>-43.7</v>
       </c>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A18" s="9">
         <v>45047</v>
       </c>
@@ -2160,7 +2160,7 @@
         <v>-38</v>
       </c>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A19" s="5">
         <v>45017</v>
       </c>
@@ -2213,7 +2213,7 @@
         <v>-37.5</v>
       </c>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A20" s="9">
         <v>44986</v>
       </c>
@@ -2266,7 +2266,7 @@
         <v>-30.4</v>
       </c>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A21" s="5">
         <v>44958</v>
       </c>
@@ -2319,7 +2319,7 @@
         <v>-20.7</v>
       </c>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A22" s="9">
         <v>44927</v>
       </c>
@@ -2372,7 +2372,7 @@
         <v>-22.2</v>
       </c>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A23" s="5">
         <v>44896</v>
       </c>
@@ -2425,7 +2425,7 @@
         <v>-3.86</v>
       </c>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A24" s="9">
         <v>44866</v>
       </c>
@@ -2478,7 +2478,7 @@
         <v>5.64</v>
       </c>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A25" s="5">
         <v>44835</v>
       </c>
@@ -2531,7 +2531,7 @@
         <v>9.19</v>
       </c>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A26" s="9">
         <v>44805</v>
       </c>
@@ -2584,7 +2584,7 @@
         <v>8.85</v>
       </c>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A27" s="5">
         <v>44774</v>
       </c>
@@ -2637,7 +2637,7 @@
         <v>11.9</v>
       </c>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A28" s="9">
         <v>44743</v>
       </c>
@@ -2690,7 +2690,7 @@
         <v>7.27</v>
       </c>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A29" s="5">
         <v>44713</v>
       </c>
@@ -2743,7 +2743,7 @@
         <v>4.41</v>
       </c>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A30" s="9">
         <v>44682</v>
       </c>
@@ -2796,7 +2796,7 @@
         <v>-0.59</v>
       </c>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A31" s="5">
         <v>44652</v>
       </c>
@@ -2849,7 +2849,7 @@
         <v>17.3</v>
       </c>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A32" s="9">
         <v>44621</v>
       </c>
@@ -2902,7 +2902,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A33" s="5">
         <v>44593</v>
       </c>
@@ -2955,7 +2955,7 @@
         <v>78.5</v>
       </c>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A34" s="9">
         <v>44562</v>
       </c>
@@ -3008,7 +3008,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A35" s="5">
         <v>44531</v>
       </c>
@@ -3061,7 +3061,7 @@
         <v>53.1</v>
       </c>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A36" s="9">
         <v>44501</v>
       </c>
@@ -3114,7 +3114,7 @@
         <v>42.6</v>
       </c>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A37" s="5">
         <v>44470</v>
       </c>
@@ -3167,7 +3167,7 @@
         <v>49.4</v>
       </c>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A38" s="9">
         <v>44440</v>
       </c>
@@ -3220,7 +3220,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A39" s="5">
         <v>44409</v>
       </c>
@@ -3273,7 +3273,7 @@
         <v>57.6</v>
       </c>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A40" s="9">
         <v>44378</v>
       </c>
@@ -3326,7 +3326,7 @@
         <v>87.1</v>
       </c>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A41" s="5">
         <v>44348</v>
       </c>
@@ -3379,7 +3379,7 @@
         <v>104.5</v>
       </c>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A42" s="9">
         <v>44317</v>
       </c>
@@ -3432,7 +3432,7 @@
         <v>92.9</v>
       </c>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A43" s="5">
         <v>44287</v>
       </c>
@@ -3485,7 +3485,7 @@
         <v>49.4</v>
       </c>
     </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A44" s="9">
         <v>44256</v>
       </c>
@@ -3538,7 +3538,7 @@
         <v>33.799999999999997</v>
       </c>
     </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A45" s="5">
         <v>44228</v>
       </c>
@@ -3591,7 +3591,7 @@
         <v>10.9</v>
       </c>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A46" s="9">
         <v>44197</v>
       </c>
@@ -3644,7 +3644,7 @@
         <v>4.01</v>
       </c>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A47" s="5">
         <v>44166</v>
       </c>
@@ -3697,7 +3697,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A48" s="9">
         <v>44136</v>
       </c>
@@ -3750,7 +3750,7 @@
         <v>45.4</v>
       </c>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A49" s="5">
         <v>44105</v>
       </c>
@@ -3803,242 +3803,242 @@
         <v>28.7</v>
       </c>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A50" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A51" s="5">
         <v>45444</v>
       </c>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A52" s="9">
         <v>45413</v>
       </c>
     </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A53" s="5">
         <v>45383</v>
       </c>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A54" s="9">
         <v>45352</v>
       </c>
     </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A55" s="5">
         <v>45323</v>
       </c>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A56" s="9">
         <v>45292</v>
       </c>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A57" s="5">
         <v>45261</v>
       </c>
     </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A58" s="9">
         <v>45231</v>
       </c>
     </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A59" s="5">
         <v>45200</v>
       </c>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A60" s="9">
         <v>45170</v>
       </c>
     </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A61" s="5">
         <v>45139</v>
       </c>
     </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A62" s="9">
         <v>45108</v>
       </c>
     </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A63" s="5">
         <v>45078</v>
       </c>
     </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A64" s="9">
         <v>45047</v>
       </c>
     </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A65" s="5">
         <v>45017</v>
       </c>
     </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A66" s="9">
         <v>44986</v>
       </c>
     </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A67" s="5">
         <v>44958</v>
       </c>
     </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A68" s="9">
         <v>44927</v>
       </c>
     </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A69" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A70" s="5">
         <v>44896</v>
       </c>
     </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A71" s="9">
         <v>44866</v>
       </c>
     </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A72" s="5">
         <v>44835</v>
       </c>
     </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A73" s="9">
         <v>44805</v>
       </c>
     </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A74" s="5">
         <v>44774</v>
       </c>
     </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A75" s="9">
         <v>44743</v>
       </c>
     </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A76" s="5">
         <v>44713</v>
       </c>
     </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A77" s="9">
         <v>44682</v>
       </c>
     </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A78" s="5">
         <v>44652</v>
       </c>
     </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A79" s="9">
         <v>44621</v>
       </c>
     </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A80" s="5">
         <v>44593</v>
       </c>
     </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A81" s="9">
         <v>44562</v>
       </c>
     </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="82" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A82" s="5">
         <v>44531</v>
       </c>
     </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="83" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A83" s="9">
         <v>44501</v>
       </c>
     </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="84" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A84" s="5">
         <v>44470</v>
       </c>
     </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="85" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A85" s="9">
         <v>44440</v>
       </c>
     </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="86" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A86" s="5">
         <v>44409</v>
       </c>
     </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="87" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A87" s="9">
         <v>44378</v>
       </c>
     </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="88" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A88" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="89" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A89" s="5">
         <v>44348</v>
       </c>
     </row>
-    <row r="90" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="90" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A90" s="9">
         <v>44317</v>
       </c>
     </row>
-    <row r="91" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="91" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A91" s="5">
         <v>44287</v>
       </c>
     </row>
-    <row r="92" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="92" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A92" s="9">
         <v>44256</v>
       </c>
     </row>
-    <row r="93" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="93" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A93" s="5">
         <v>44228</v>
       </c>
     </row>
-    <row r="94" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="94" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A94" s="9">
         <v>44197</v>
       </c>
     </row>
-    <row r="95" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="95" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A95" s="5">
         <v>44166</v>
       </c>
     </row>
-    <row r="96" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="96" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A96" s="9">
         <v>44136</v>
       </c>
     </row>
-    <row r="97" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="97" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A97" s="5">
         <v>44105</v>
       </c>
